--- a/verification/cases/roundtrip/rk_number/init.xlsx
+++ b/verification/cases/roundtrip/rk_number/init.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="24030"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" showInkAnnotation="0" autoCompressPictures="0"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E015137-D9C9-41B4-AD0D-28DEA06CF471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16080" yWindow="5620" windowWidth="8800" windowHeight="11240" tabRatio="500"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RkNumber" sheetId="1" r:id="rId1"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -78,6 +79,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -402,14 +411,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -420,7 +429,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -431,7 +440,7 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -442,7 +451,7 @@
         <v>1200455</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -453,7 +462,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
